--- a/static/standards-correlations/Nebraska_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Nebraska_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$35</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Nebraska CS and Technology Standards</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Nebraska CS and Technology Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Ext 4.2E (A Basic Building Block of AI) names transport and aviation applications, Discovery Coding 2 covers how professional programmers work, and Ext 5.3H (Find the Community) exposes students to practitioner repositories. Industry survey and career pathways are not taught.</t>
+          <t>Ext 4.2E (A Basic Building Block of AI) names transport and aviation applications, Introductory Coding 2 covers how professional programmers work, and Ext 5.3H (Find the Community) exposes students to practitioner repositories. Industry survey and career pathways are not taught.</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1035,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) evaluates credential strength, Ext 5.3G (Secret Messages / HTTPS) evaluates transport protection, and Ext 5.3H (Find the Community) plus Discovery Systems 11 cover the visible, lasting record a public repository creates.</t>
+          <t>Ext 1.1F (Why a PIN?) evaluates credential strength, Ext 5.3G (Secret Messages / HTTPS) evaluates transport protection, and Ext 5.3H (Find the Community) plus Introductory Systems 11 cover the visible, lasting record a public repository creates.</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1246,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Discovery Systems 9 covers senders, receivers, and protocols. Routers, switches, and addressing are absent.</t>
+          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Introductory Systems 9 covers senders, receivers, and protocols. Routers, switches, and addressing are absent.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1414,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) covers credential strength, Ext 5.3G (Secret Messages / HTTPS) covers protected transport, and Discovery Systems 10 covers recognising manipulation. Three distinct protection methods are identified.</t>
+          <t>Ext 1.1F (Why a PIN?) covers credential strength, Ext 5.3G (Secret Messages / HTTPS) covers protected transport, and Introductory Systems 10 covers recognising manipulation. Three distinct protection methods are identified.</t>
         </is>
       </c>
     </row>
@@ -1943,6 +1944,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1987,7 +1989,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2001,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2099,6 +2101,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -2116,7 +2120,7 @@
 SOURCE NOTE: Standard codes and statements transcribed from the CodeHS published Nebraska Computer Science and Technology standards framework. Verify wording against the official NDE standards document before using this crosswalk in any formal submission. Strand titles in column B are descriptive labels assigned for this crosswalk; the source provides numeric standards only.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
